--- a/Excel/ActivityConfig.xlsx
+++ b/Excel/ActivityConfig.xlsx
@@ -1295,7 +1295,7 @@
     <t>Mid-Autumn Festival</t>
   </si>
   <si>
-    <t>10;6</t>
+    <t>9;25</t>
   </si>
   <si>
     <t>中秋节</t>
@@ -3538,7 +3538,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{BF3D6FC4-1B52-4362-BC49-AB844017F6F3}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{053FB007-AA64-43B1-BA31-902EBA99BBB5}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
